--- a/crm-system-backend/src/main/resources/templates/Report Template.xlsx
+++ b/crm-system-backend/src/main/resources/templates/Report Template.xlsx
@@ -7,16 +7,18 @@
   </bookViews>
   <sheets>
     <sheet name="Summary Report" r:id="rId3" sheetId="1"/>
-    <sheet name="Akanksha Senad" r:id="rId4" sheetId="2"/>
-    <sheet name="Sayali Sonawane" r:id="rId5" sheetId="3"/>
+    <sheet name="Bhagyashri Mahajan" r:id="rId4" sheetId="2"/>
+    <sheet name="Akanksha Senad" r:id="rId5" sheetId="3"/>
+    <sheet name="Purva Patil" r:id="rId6" sheetId="4"/>
+    <sheet name="Sayali Sonawane" r:id="rId7" sheetId="5"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="38">
-  <si>
-    <t xml:space="preserve"> From: 2025-02-01, To: 2025-10-31</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="38">
+  <si>
+    <t xml:space="preserve"> From: 2025-01-01, To: 2025-01-31</t>
   </si>
   <si>
     <t>Sr No</t>
@@ -46,19 +48,28 @@
     <t>Comment</t>
   </si>
   <si>
+    <t>Bhagyashri Mahajan</t>
+  </si>
+  <si>
+    <t>bha@gmail.com</t>
+  </si>
+  <si>
+    <t>0.00 %</t>
+  </si>
+  <si>
+    <t>Leads neither Processed nor Converted: 0</t>
+  </si>
+  <si>
     <t>Akanksha Senad</t>
   </si>
   <si>
     <t>aka@gmail.com</t>
   </si>
   <si>
-    <t>50.00 %</t>
-  </si>
-  <si>
-    <t>0.00 %</t>
-  </si>
-  <si>
-    <t>Leads neither Processed nor Converted: 1</t>
+    <t>Purva Patil</t>
+  </si>
+  <si>
+    <t>pur@gmail.com</t>
   </si>
   <si>
     <t>Sayali Sonawane</t>
@@ -67,12 +78,6 @@
     <t>say@gmail.com</t>
   </si>
   <si>
-    <t>100.00 %</t>
-  </si>
-  <si>
-    <t>Leads neither Processed nor Converted: 0</t>
-  </si>
-  <si>
     <t>Lead ID</t>
   </si>
   <si>
@@ -91,43 +96,40 @@
     <t>Status</t>
   </si>
   <si>
-    <t>fgh</t>
-  </si>
-  <si>
-    <t>ij</t>
-  </si>
-  <si>
-    <t>fgh@gmail.com</t>
-  </si>
-  <si>
-    <t>GSTIN9393932</t>
-  </si>
-  <si>
-    <t>LMS</t>
-  </si>
-  <si>
-    <t>CONTACTED</t>
-  </si>
-  <si>
-    <t>ITC Reconciliation</t>
-  </si>
-  <si>
-    <t>klm</t>
-  </si>
-  <si>
-    <t>no</t>
-  </si>
-  <si>
-    <t>klm@gmail.com</t>
-  </si>
-  <si>
-    <t>GSTIN9393933</t>
-  </si>
-  <si>
-    <t>E-Invoice</t>
-  </si>
-  <si>
-    <t>CONVERTED</t>
+    <t>Akanksha</t>
+  </si>
+  <si>
+    <t>LeadOne</t>
+  </si>
+  <si>
+    <t>alead1@gmail.com</t>
+  </si>
+  <si>
+    <t>GSTIN9999999901</t>
+  </si>
+  <si>
+    <t>ITC Reconsilation</t>
+  </si>
+  <si>
+    <t>ADDED</t>
+  </si>
+  <si>
+    <t>GSTR</t>
+  </si>
+  <si>
+    <t>Sayali</t>
+  </si>
+  <si>
+    <t>slead1@gmail.com</t>
+  </si>
+  <si>
+    <t>GSTIN7777777701</t>
+  </si>
+  <si>
+    <t>E Invoice</t>
+  </si>
+  <si>
+    <t>Third Eye</t>
   </si>
 </sst>
 </file>
@@ -218,12 +220,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I8"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="5.38671875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="14.2734375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="13.78515625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="17.21484375" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="14.015625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="20.96875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="23.86328125" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="24.1328125" customWidth="true" bestFit="true"/>
@@ -280,7 +282,7 @@
         <v>2.0</v>
       </c>
       <c r="E5" t="n" s="0">
-        <v>1.0</v>
+        <v>0.0</v>
       </c>
       <c r="F5" t="n" s="0">
         <v>0.0</v>
@@ -289,10 +291,10 @@
         <v>12</v>
       </c>
       <c r="H5" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="I5" t="s" s="0">
         <v>13</v>
-      </c>
-      <c r="I5" t="s" s="0">
-        <v>14</v>
       </c>
     </row>
     <row r="6" s="3" customFormat="true">
@@ -300,28 +302,86 @@
         <v>2.0</v>
       </c>
       <c r="B6" t="s" s="0">
+        <v>14</v>
+      </c>
+      <c r="C6" t="s" s="0">
         <v>15</v>
       </c>
-      <c r="C6" t="s" s="0">
+      <c r="D6" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="F6" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="H6" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="I6" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="7" s="3" customFormat="true">
+      <c r="A7" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B7" t="s" s="0">
         <v>16</v>
       </c>
-      <c r="D6" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="E6" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="F6" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="G6" t="s" s="0">
+      <c r="C7" t="s" s="0">
         <v>17</v>
       </c>
-      <c r="H6" t="s" s="0">
-        <v>17</v>
-      </c>
-      <c r="I6" t="s" s="0">
+      <c r="D7" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="F7" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="H7" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="I7" t="s" s="0">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" s="3" customFormat="true">
+      <c r="A8" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B8" t="s" s="0">
         <v>18</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="I8" t="s" s="0">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
@@ -343,16 +403,16 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.0234375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="9.828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.54296875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.56640625" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="12.8125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="15.1796875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="10.85546875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="5.45703125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="5.94140625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="8.171875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="6.06640625" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -360,71 +420,25 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s" s="2">
         <v>3</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" s="3" customFormat="true">
-      <c r="A4" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="B4" t="s" s="0">
         <v>25</v>
-      </c>
-      <c r="C4" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="E4" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="F4" t="s" s="0">
-        <v>29</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" s="3" customFormat="true">
-      <c r="A5" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="B5" t="s" s="0">
-        <v>25</v>
-      </c>
-      <c r="C5" t="s" s="0">
-        <v>26</v>
-      </c>
-      <c r="D5" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="E5" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="F5" t="s" s="0">
-        <v>31</v>
-      </c>
-      <c r="G5" t="s" s="0">
-        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -437,16 +451,16 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="7.0234375" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="9.828125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="9.54296875" customWidth="true" bestFit="true"/>
-    <col min="4" max="4" width="13.92578125" customWidth="true" bestFit="true"/>
-    <col min="5" max="5" width="12.8125" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="8.23046875" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="10.85546875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="16.359375" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="15.8125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="14.6640625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="6.67578125" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -454,25 +468,25 @@
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s" s="2">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D3" t="s" s="2">
         <v>3</v>
       </c>
       <c r="E3" t="s" s="2">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="F3" t="s" s="2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="G3" t="s" s="2">
-        <v>24</v>
+        <v>25</v>
       </c>
     </row>
     <row r="4" s="3" customFormat="true">
@@ -480,10 +494,152 @@
         <v>3.0</v>
       </c>
       <c r="B4" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D4" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E4" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" s="3" customFormat="true">
+      <c r="A5" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>28</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="F5" t="s" s="0">
         <v>32</v>
       </c>
+      <c r="G5" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G2"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G3"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="7.0234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="9.828125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.54296875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="5.45703125" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="5.94140625" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="8.171875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="6.06640625" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:G2"/>
+  </mergeCells>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:G5"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="7.0234375" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="9.828125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="9.54296875" customWidth="true" bestFit="true"/>
+    <col min="4" max="4" width="16.1875" customWidth="true" bestFit="true"/>
+    <col min="5" max="5" width="15.8125" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="8.390625" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="6.67578125" customWidth="true" bestFit="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>20</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="C3" t="s" s="2">
+        <v>22</v>
+      </c>
+      <c r="D3" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="E3" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F3" t="s" s="2">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s" s="2">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" s="3" customFormat="true">
+      <c r="A4" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>33</v>
+      </c>
       <c r="C4" t="s" s="0">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="D4" t="s" s="0">
         <v>34</v>
@@ -495,7 +651,30 @@
         <v>36</v>
       </c>
       <c r="G4" t="s" s="0">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="5" s="3" customFormat="true">
+      <c r="A5" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D5" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="E5" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="F5" t="s" s="0">
         <v>37</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>31</v>
       </c>
     </row>
   </sheetData>
